--- a/French Ligue 1/Y.xlsx
+++ b/French Ligue 1/Y.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2379"/>
+  <dimension ref="A1:C2388"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25659,57 +25659,57 @@
     </row>
     <row r="2294">
       <c r="A2294" t="n">
-        <v>0.4327036516882931</v>
+        <v>0.5642880041507895</v>
       </c>
       <c r="B2294" t="n">
-        <v>0.2616165774780552</v>
+        <v>0.2476772037078476</v>
       </c>
       <c r="C2294" t="n">
-        <v>0.3056797708336517</v>
+        <v>0.188034792141363</v>
       </c>
     </row>
     <row r="2295">
       <c r="A2295" t="n">
-        <v>0.5642880041507895</v>
+        <v>0.6588361633666832</v>
       </c>
       <c r="B2295" t="n">
-        <v>0.2476772037078476</v>
+        <v>0.187230153603718</v>
       </c>
       <c r="C2295" t="n">
-        <v>0.188034792141363</v>
+        <v>0.1539336830295989</v>
       </c>
     </row>
     <row r="2296">
       <c r="A2296" t="n">
-        <v>0.6588361633666832</v>
+        <v>0.3465420251613687</v>
       </c>
       <c r="B2296" t="n">
-        <v>0.187230153603718</v>
+        <v>0.2589809258551041</v>
       </c>
       <c r="C2296" t="n">
-        <v>0.1539336830295989</v>
+        <v>0.3944770489835272</v>
       </c>
     </row>
     <row r="2297">
       <c r="A2297" t="n">
-        <v>0.3465420251613687</v>
+        <v>0.1713834109526946</v>
       </c>
       <c r="B2297" t="n">
-        <v>0.2589809258551041</v>
+        <v>0.2235194647700192</v>
       </c>
       <c r="C2297" t="n">
-        <v>0.3944770489835272</v>
+        <v>0.6050971242772861</v>
       </c>
     </row>
     <row r="2298">
       <c r="A2298" t="n">
-        <v>0.1713834109526946</v>
+        <v>0.05403746878693977</v>
       </c>
       <c r="B2298" t="n">
-        <v>0.2235194647700192</v>
+        <v>0.09909260153292203</v>
       </c>
       <c r="C2298" t="n">
-        <v>0.6050971242772861</v>
+        <v>0.8468699296801383</v>
       </c>
     </row>
     <row r="2299">
@@ -25747,859 +25747,958 @@
     </row>
     <row r="2302">
       <c r="A2302" t="n">
-        <v>0.2255109460456201</v>
+        <v>0.5469503013526338</v>
       </c>
       <c r="B2302" t="n">
-        <v>0.2668525441058884</v>
+        <v>0.2452132810015607</v>
       </c>
       <c r="C2302" t="n">
-        <v>0.5076365098484914</v>
+        <v>0.2078364176458055</v>
       </c>
     </row>
     <row r="2303">
       <c r="A2303" t="n">
-        <v>0.4748916486342835</v>
+        <v>0.2255109460456201</v>
       </c>
       <c r="B2303" t="n">
-        <v>0.2720149465757925</v>
+        <v>0.2668525441058884</v>
       </c>
       <c r="C2303" t="n">
-        <v>0.2530934047899241</v>
+        <v>0.5076365098484914</v>
       </c>
     </row>
     <row r="2304">
       <c r="A2304" t="n">
-        <v>0.637594464770934</v>
+        <v>0.4748916486342835</v>
       </c>
       <c r="B2304" t="n">
-        <v>0.2181696887098385</v>
+        <v>0.2720149465757925</v>
       </c>
       <c r="C2304" t="n">
-        <v>0.1442358465192274</v>
+        <v>0.2530934047899241</v>
       </c>
     </row>
     <row r="2305">
       <c r="A2305" t="n">
-        <v>0.8527815466094063</v>
+        <v>0.637594464770934</v>
       </c>
       <c r="B2305" t="n">
-        <v>0.09775034246993393</v>
+        <v>0.2181696887098385</v>
       </c>
       <c r="C2305" t="n">
-        <v>0.04946811092065981</v>
+        <v>0.1442358465192274</v>
       </c>
     </row>
     <row r="2306">
       <c r="A2306" t="n">
-        <v>0.2436373934230274</v>
+        <v>0.8527815466094063</v>
       </c>
       <c r="B2306" t="n">
-        <v>0.2567930388063777</v>
+        <v>0.09775034246993393</v>
       </c>
       <c r="C2306" t="n">
-        <v>0.4995695677705947</v>
+        <v>0.04946811092065981</v>
       </c>
     </row>
     <row r="2307">
       <c r="A2307" t="n">
-        <v>0.4227499799165122</v>
+        <v>0.2436373934230274</v>
       </c>
       <c r="B2307" t="n">
-        <v>0.268130926488484</v>
+        <v>0.2567930388063777</v>
       </c>
       <c r="C2307" t="n">
-        <v>0.3091190935950038</v>
+        <v>0.4995695677705947</v>
       </c>
     </row>
     <row r="2308">
       <c r="A2308" t="n">
-        <v>0.5184818727896096</v>
+        <v>0.4227499799165122</v>
       </c>
       <c r="B2308" t="n">
-        <v>0.2593793458643162</v>
+        <v>0.268130926488484</v>
       </c>
       <c r="C2308" t="n">
-        <v>0.2221387813460741</v>
+        <v>0.3091190935950038</v>
       </c>
     </row>
     <row r="2309">
       <c r="A2309" t="n">
-        <v>0.2832136686593894</v>
+        <v>0.6121363675552758</v>
       </c>
       <c r="B2309" t="n">
-        <v>0.270541916146665</v>
+        <v>0.2185809520347468</v>
       </c>
       <c r="C2309" t="n">
-        <v>0.4462444151939455</v>
+        <v>0.1692826804099774</v>
       </c>
     </row>
     <row r="2310">
       <c r="A2310" t="n">
-        <v>0.544524481243983</v>
+        <v>0.5184818727896096</v>
       </c>
       <c r="B2310" t="n">
-        <v>0.2471580808906719</v>
+        <v>0.2593793458643162</v>
       </c>
       <c r="C2310" t="n">
-        <v>0.2083174378653452</v>
+        <v>0.2221387813460741</v>
       </c>
     </row>
     <row r="2311">
       <c r="A2311" t="n">
-        <v>0.6233541761115986</v>
+        <v>0.2832136686593894</v>
       </c>
       <c r="B2311" t="n">
-        <v>0.2285730036992507</v>
+        <v>0.270541916146665</v>
       </c>
       <c r="C2311" t="n">
-        <v>0.1480728201891507</v>
+        <v>0.4462444151939455</v>
       </c>
     </row>
     <row r="2312">
       <c r="A2312" t="n">
-        <v>0.4716943912293014</v>
+        <v>0.3943732863354975</v>
       </c>
       <c r="B2312" t="n">
-        <v>0.2473195374392241</v>
+        <v>0.277915578501334</v>
       </c>
       <c r="C2312" t="n">
-        <v>0.2809860713314745</v>
+        <v>0.3277111351631686</v>
       </c>
     </row>
     <row r="2313">
       <c r="A2313" t="n">
-        <v>0.3329994764022534</v>
+        <v>0.544524481243983</v>
       </c>
       <c r="B2313" t="n">
-        <v>0.2908248728483065</v>
+        <v>0.2471580808906719</v>
       </c>
       <c r="C2313" t="n">
-        <v>0.37617565074944</v>
+        <v>0.2083174378653452</v>
       </c>
     </row>
     <row r="2314">
       <c r="A2314" t="n">
-        <v>0.3747621813353075</v>
+        <v>0.6233541761115986</v>
       </c>
       <c r="B2314" t="n">
-        <v>0.2793446213409493</v>
+        <v>0.2285730036992507</v>
       </c>
       <c r="C2314" t="n">
-        <v>0.3458931973237431</v>
+        <v>0.1480728201891507</v>
       </c>
     </row>
     <row r="2315">
       <c r="A2315" t="n">
-        <v>0.2663483659081898</v>
+        <v>0.4716943912293014</v>
       </c>
       <c r="B2315" t="n">
-        <v>0.2781282764049908</v>
+        <v>0.2473195374392241</v>
       </c>
       <c r="C2315" t="n">
-        <v>0.4555233576868193</v>
+        <v>0.2809860713314745</v>
       </c>
     </row>
     <row r="2316">
       <c r="A2316" t="n">
-        <v>0.269391248291116</v>
+        <v>0.3329994764022534</v>
       </c>
       <c r="B2316" t="n">
-        <v>0.2525191450578519</v>
+        <v>0.2908248728483065</v>
       </c>
       <c r="C2316" t="n">
-        <v>0.478089606651032</v>
+        <v>0.37617565074944</v>
       </c>
     </row>
     <row r="2317">
       <c r="A2317" t="n">
-        <v>0.5294239837043045</v>
+        <v>0.3747621813353075</v>
       </c>
       <c r="B2317" t="n">
-        <v>0.2618564148095185</v>
+        <v>0.2793446213409493</v>
       </c>
       <c r="C2317" t="n">
-        <v>0.2087196014861769</v>
+        <v>0.3458931973237431</v>
       </c>
     </row>
     <row r="2318">
       <c r="A2318" t="n">
-        <v>0.8548141587290957</v>
+        <v>0.2741836034362178</v>
       </c>
       <c r="B2318" t="n">
-        <v>0.09123157500152693</v>
+        <v>0.2631805737972373</v>
       </c>
       <c r="C2318" t="n">
-        <v>0.0539542662693773</v>
+        <v>0.4626358227665449</v>
       </c>
     </row>
     <row r="2319">
       <c r="A2319" t="n">
-        <v>0.6116499625981382</v>
+        <v>0.4963453287192592</v>
       </c>
       <c r="B2319" t="n">
-        <v>0.203969275048536</v>
+        <v>0.2637257196192249</v>
       </c>
       <c r="C2319" t="n">
-        <v>0.184380762353326</v>
+        <v>0.2399289516615159</v>
       </c>
     </row>
     <row r="2320">
       <c r="A2320" t="n">
-        <v>0.6373133460018686</v>
+        <v>0.2663483659081898</v>
       </c>
       <c r="B2320" t="n">
-        <v>0.222271061552439</v>
+        <v>0.2781282764049908</v>
       </c>
       <c r="C2320" t="n">
-        <v>0.1404155924456925</v>
+        <v>0.4555233576868193</v>
       </c>
     </row>
     <row r="2321">
       <c r="A2321" t="n">
-        <v>0.4021775390639665</v>
+        <v>0.269391248291116</v>
       </c>
       <c r="B2321" t="n">
-        <v>0.2862837748484922</v>
+        <v>0.2525191450578519</v>
       </c>
       <c r="C2321" t="n">
-        <v>0.3115386860875413</v>
+        <v>0.478089606651032</v>
       </c>
     </row>
     <row r="2322">
       <c r="A2322" t="n">
-        <v>0.6944768060931765</v>
+        <v>0.5294239837043045</v>
       </c>
       <c r="B2322" t="n">
-        <v>0.1899983714783219</v>
+        <v>0.2618564148095185</v>
       </c>
       <c r="C2322" t="n">
-        <v>0.1155248224285016</v>
+        <v>0.2087196014861769</v>
       </c>
     </row>
     <row r="2323">
       <c r="A2323" t="n">
-        <v>0.2902043165596522</v>
+        <v>0.8548141587290957</v>
       </c>
       <c r="B2323" t="n">
-        <v>0.2844172510094891</v>
+        <v>0.09123157500152693</v>
       </c>
       <c r="C2323" t="n">
-        <v>0.4253784324308585</v>
+        <v>0.0539542662693773</v>
       </c>
     </row>
     <row r="2324">
       <c r="A2324" t="n">
-        <v>0.1382412750803896</v>
+        <v>0.6116499625981382</v>
       </c>
       <c r="B2324" t="n">
-        <v>0.1805104074683681</v>
+        <v>0.203969275048536</v>
       </c>
       <c r="C2324" t="n">
-        <v>0.6812483174512423</v>
+        <v>0.184380762353326</v>
       </c>
     </row>
     <row r="2325">
       <c r="A2325" t="n">
-        <v>0.5642340971254031</v>
+        <v>0.7950121165414604</v>
       </c>
       <c r="B2325" t="n">
-        <v>0.2155894466853268</v>
+        <v>0.1331223813982946</v>
       </c>
       <c r="C2325" t="n">
-        <v>0.22017645618927</v>
+        <v>0.07186550206024499</v>
       </c>
     </row>
     <row r="2326">
       <c r="A2326" t="n">
-        <v>0.1379284497853253</v>
+        <v>0.6373133460018686</v>
       </c>
       <c r="B2326" t="n">
-        <v>0.1878403012640618</v>
+        <v>0.222271061552439</v>
       </c>
       <c r="C2326" t="n">
-        <v>0.6742312489506127</v>
+        <v>0.1404155924456925</v>
       </c>
     </row>
     <row r="2327">
       <c r="A2327" t="n">
-        <v>0.542990387164357</v>
+        <v>0.4021775390639665</v>
       </c>
       <c r="B2327" t="n">
-        <v>0.2327473163372124</v>
+        <v>0.2862837748484922</v>
       </c>
       <c r="C2327" t="n">
-        <v>0.2242622964984307</v>
+        <v>0.3115386860875413</v>
       </c>
     </row>
     <row r="2328">
       <c r="A2328" t="n">
-        <v>0.1549937142058947</v>
+        <v>0.6944768060931765</v>
       </c>
       <c r="B2328" t="n">
-        <v>0.2372677748288867</v>
+        <v>0.1899983714783219</v>
       </c>
       <c r="C2328" t="n">
-        <v>0.6077385109652186</v>
+        <v>0.1155248224285016</v>
       </c>
     </row>
     <row r="2329">
       <c r="A2329" t="n">
-        <v>0.3226002885010074</v>
+        <v>0.2902043165596522</v>
       </c>
       <c r="B2329" t="n">
-        <v>0.2919786166179009</v>
+        <v>0.2844172510094891</v>
       </c>
       <c r="C2329" t="n">
-        <v>0.3854210948810918</v>
+        <v>0.4253784324308585</v>
       </c>
     </row>
     <row r="2330">
       <c r="A2330" t="n">
-        <v>0.6013387876534028</v>
+        <v>0.1923971740308457</v>
       </c>
       <c r="B2330" t="n">
-        <v>0.2242469319449609</v>
+        <v>0.2154132294089265</v>
       </c>
       <c r="C2330" t="n">
-        <v>0.1744142804016363</v>
+        <v>0.592189596560228</v>
       </c>
     </row>
     <row r="2331">
       <c r="A2331" t="n">
-        <v>0.6410441497470536</v>
+        <v>0.1382412750803896</v>
       </c>
       <c r="B2331" t="n">
-        <v>0.204819438450709</v>
+        <v>0.1805104074683681</v>
       </c>
       <c r="C2331" t="n">
-        <v>0.1541364118022374</v>
+        <v>0.6812483174512423</v>
       </c>
     </row>
     <row r="2332">
       <c r="A2332" t="n">
-        <v>0.6806010361843775</v>
+        <v>0.5642340971254031</v>
       </c>
       <c r="B2332" t="n">
-        <v>0.1903854340650096</v>
+        <v>0.2155894466853268</v>
       </c>
       <c r="C2332" t="n">
-        <v>0.1290135297506129</v>
+        <v>0.22017645618927</v>
       </c>
     </row>
     <row r="2333">
       <c r="A2333" t="n">
-        <v>0.3877166848679393</v>
+        <v>0.5873440693675855</v>
       </c>
       <c r="B2333" t="n">
-        <v>0.2453580839088525</v>
+        <v>0.2188300411807062</v>
       </c>
       <c r="C2333" t="n">
-        <v>0.3669252312232083</v>
+        <v>0.1938258894517082</v>
       </c>
     </row>
     <row r="2334">
       <c r="A2334" t="n">
-        <v>0.4469967338716719</v>
+        <v>0.1379284497853253</v>
       </c>
       <c r="B2334" t="n">
-        <v>0.2784738273085589</v>
+        <v>0.1878403012640618</v>
       </c>
       <c r="C2334" t="n">
-        <v>0.2745294388197691</v>
+        <v>0.6742312489506127</v>
       </c>
     </row>
     <row r="2335">
       <c r="A2335" t="n">
-        <v>0.1405184366219548</v>
+        <v>0.542990387164357</v>
       </c>
       <c r="B2335" t="n">
-        <v>0.1780770819495331</v>
+        <v>0.2327473163372124</v>
       </c>
       <c r="C2335" t="n">
-        <v>0.6814044814285122</v>
+        <v>0.2242622964984307</v>
       </c>
     </row>
     <row r="2336">
       <c r="A2336" t="n">
-        <v>0.5067770564132954</v>
+        <v>0.1549937142058947</v>
       </c>
       <c r="B2336" t="n">
-        <v>0.2792801229372925</v>
+        <v>0.2372677748288867</v>
       </c>
       <c r="C2336" t="n">
-        <v>0.2139428206494123</v>
+        <v>0.6077385109652186</v>
       </c>
     </row>
     <row r="2337">
       <c r="A2337" t="n">
-        <v>0.7011667776198328</v>
+        <v>0.3226002885010074</v>
       </c>
       <c r="B2337" t="n">
-        <v>0.1820286020271533</v>
+        <v>0.2919786166179009</v>
       </c>
       <c r="C2337" t="n">
-        <v>0.1168046203530137</v>
+        <v>0.3854210948810918</v>
       </c>
     </row>
     <row r="2338">
       <c r="A2338" t="n">
-        <v>0.6211638987885926</v>
+        <v>0.6013387876534028</v>
       </c>
       <c r="B2338" t="n">
-        <v>0.2089320713110163</v>
+        <v>0.2242469319449609</v>
       </c>
       <c r="C2338" t="n">
-        <v>0.169904029900391</v>
+        <v>0.1744142804016363</v>
       </c>
     </row>
     <row r="2339">
       <c r="A2339" t="n">
-        <v>0.4515537304485305</v>
+        <v>0.2157934530732292</v>
       </c>
       <c r="B2339" t="n">
-        <v>0.265532418563261</v>
+        <v>0.2495076914737027</v>
       </c>
       <c r="C2339" t="n">
-        <v>0.2829138509882085</v>
+        <v>0.5346988554530681</v>
       </c>
     </row>
     <row r="2340">
       <c r="A2340" t="n">
-        <v>0.4070040005863193</v>
+        <v>0.6410441497470536</v>
       </c>
       <c r="B2340" t="n">
-        <v>0.2849508528307997</v>
+        <v>0.204819438450709</v>
       </c>
       <c r="C2340" t="n">
-        <v>0.3080451465828811</v>
+        <v>0.1541364118022374</v>
       </c>
     </row>
     <row r="2341">
       <c r="A2341" t="n">
-        <v>0.4595244589119757</v>
+        <v>0.6806010361843775</v>
       </c>
       <c r="B2341" t="n">
-        <v>0.2570886172792867</v>
+        <v>0.1903854340650096</v>
       </c>
       <c r="C2341" t="n">
-        <v>0.2833869238087375</v>
+        <v>0.1290135297506129</v>
       </c>
     </row>
     <row r="2342">
       <c r="A2342" t="n">
-        <v>0.2605002963567936</v>
+        <v>0.3877166848679393</v>
       </c>
       <c r="B2342" t="n">
-        <v>0.2547448979101942</v>
+        <v>0.2453580839088525</v>
       </c>
       <c r="C2342" t="n">
-        <v>0.4847548057330123</v>
+        <v>0.3669252312232083</v>
       </c>
     </row>
     <row r="2343">
       <c r="A2343" t="n">
-        <v>0.2186995701664953</v>
+        <v>0.4469967338716719</v>
       </c>
       <c r="B2343" t="n">
-        <v>0.2554197840133062</v>
+        <v>0.2784738273085589</v>
       </c>
       <c r="C2343" t="n">
-        <v>0.5258806458201986</v>
+        <v>0.2745294388197691</v>
       </c>
     </row>
     <row r="2344">
       <c r="A2344" t="n">
-        <v>0.1602662855247951</v>
+        <v>0.1405184366219548</v>
       </c>
       <c r="B2344" t="n">
-        <v>0.2097286155177097</v>
+        <v>0.1780770819495331</v>
       </c>
       <c r="C2344" t="n">
-        <v>0.6300050989574952</v>
+        <v>0.6814044814285122</v>
       </c>
     </row>
     <row r="2345">
       <c r="A2345" t="n">
-        <v>0.3310799934134086</v>
+        <v>0.5067770564132954</v>
       </c>
       <c r="B2345" t="n">
-        <v>0.2752397210200361</v>
+        <v>0.2792801229372925</v>
       </c>
       <c r="C2345" t="n">
-        <v>0.3936802855665552</v>
+        <v>0.2139428206494123</v>
       </c>
     </row>
     <row r="2346">
       <c r="A2346" t="n">
-        <v>0.5241871707417967</v>
+        <v>0.7011667776198328</v>
       </c>
       <c r="B2346" t="n">
-        <v>0.2266888233695762</v>
+        <v>0.1820286020271533</v>
       </c>
       <c r="C2346" t="n">
-        <v>0.2491240058886271</v>
+        <v>0.1168046203530137</v>
       </c>
     </row>
     <row r="2347">
       <c r="A2347" t="n">
-        <v>0.4206745219724419</v>
+        <v>0.6211638987885926</v>
       </c>
       <c r="B2347" t="n">
-        <v>0.271991925987819</v>
+        <v>0.2089320713110163</v>
       </c>
       <c r="C2347" t="n">
-        <v>0.3073335520397393</v>
+        <v>0.169904029900391</v>
       </c>
     </row>
     <row r="2348">
       <c r="A2348" t="n">
-        <v>0.09422290416605195</v>
+        <v>0.4515537304485305</v>
       </c>
       <c r="B2348" t="n">
-        <v>0.1301690684095619</v>
+        <v>0.265532418563261</v>
       </c>
       <c r="C2348" t="n">
-        <v>0.7756080274243863</v>
+        <v>0.2829138509882085</v>
       </c>
     </row>
     <row r="2349">
       <c r="A2349" t="n">
-        <v>0.2095047077453025</v>
+        <v>0.4070040005863193</v>
       </c>
       <c r="B2349" t="n">
-        <v>0.2482339508351911</v>
+        <v>0.2849508528307997</v>
       </c>
       <c r="C2349" t="n">
-        <v>0.5422613414195063</v>
+        <v>0.3080451465828811</v>
       </c>
     </row>
     <row r="2350">
       <c r="A2350" t="n">
-        <v>0.6896309089660234</v>
+        <v>0.4595244589119757</v>
       </c>
       <c r="B2350" t="n">
-        <v>0.1944898482659735</v>
+        <v>0.2570886172792867</v>
       </c>
       <c r="C2350" t="n">
-        <v>0.115879242768003</v>
+        <v>0.2833869238087375</v>
       </c>
     </row>
     <row r="2351">
       <c r="A2351" t="n">
-        <v>0.2389642734729595</v>
+        <v>0.2605002963567936</v>
       </c>
       <c r="B2351" t="n">
-        <v>0.2401502003884581</v>
+        <v>0.2547448979101942</v>
       </c>
       <c r="C2351" t="n">
-        <v>0.5208855261385824</v>
+        <v>0.4847548057330123</v>
       </c>
     </row>
     <row r="2352">
       <c r="A2352" t="n">
-        <v>0.6239036311688189</v>
+        <v>0.2186995701664953</v>
       </c>
       <c r="B2352" t="n">
-        <v>0.2140297210063437</v>
+        <v>0.2554197840133062</v>
       </c>
       <c r="C2352" t="n">
-        <v>0.1620666478248375</v>
+        <v>0.5258806458201986</v>
       </c>
     </row>
     <row r="2353">
       <c r="A2353" t="n">
-        <v>0.8060310558861845</v>
+        <v>0.1602662855247951</v>
       </c>
       <c r="B2353" t="n">
-        <v>0.1212900280372265</v>
+        <v>0.2097286155177097</v>
       </c>
       <c r="C2353" t="n">
-        <v>0.07267891607658901</v>
+        <v>0.6300050989574952</v>
       </c>
     </row>
     <row r="2354">
       <c r="A2354" t="n">
-        <v>0.6097629175489302</v>
+        <v>0.3310799934134086</v>
       </c>
       <c r="B2354" t="n">
-        <v>0.2013872516831749</v>
+        <v>0.2752397210200361</v>
       </c>
       <c r="C2354" t="n">
-        <v>0.188849830767895</v>
+        <v>0.3936802855665552</v>
       </c>
     </row>
     <row r="2355">
       <c r="A2355" t="n">
-        <v>0.7508040831582646</v>
+        <v>0.5241871707417967</v>
       </c>
       <c r="B2355" t="n">
-        <v>0.1539124321656916</v>
+        <v>0.2266888233695762</v>
       </c>
       <c r="C2355" t="n">
-        <v>0.09528348467604388</v>
+        <v>0.2491240058886271</v>
       </c>
     </row>
     <row r="2356">
       <c r="A2356" t="n">
-        <v>0.6463291238137986</v>
+        <v>0.4206745219724419</v>
       </c>
       <c r="B2356" t="n">
-        <v>0.2008352144296621</v>
+        <v>0.271991925987819</v>
       </c>
       <c r="C2356" t="n">
-        <v>0.1528356617565393</v>
+        <v>0.3073335520397393</v>
       </c>
     </row>
     <row r="2357">
       <c r="A2357" t="n">
-        <v>0.5318044025338795</v>
+        <v>0.09422290416605195</v>
       </c>
       <c r="B2357" t="n">
-        <v>0.2368211856305849</v>
+        <v>0.1301690684095619</v>
       </c>
       <c r="C2357" t="n">
-        <v>0.2313744118355355</v>
+        <v>0.7756080274243863</v>
       </c>
     </row>
     <row r="2358">
       <c r="A2358" t="n">
-        <v>0.4648062809942835</v>
+        <v>0.2095047077453025</v>
       </c>
       <c r="B2358" t="n">
-        <v>0.2336061685185387</v>
+        <v>0.2482339508351911</v>
       </c>
       <c r="C2358" t="n">
-        <v>0.3015875504871778</v>
+        <v>0.5422613414195063</v>
       </c>
     </row>
     <row r="2359">
       <c r="A2359" t="n">
-        <v>0.2733245367333059</v>
+        <v>0.6896309089660234</v>
       </c>
       <c r="B2359" t="n">
-        <v>0.2666716068331038</v>
+        <v>0.1944898482659735</v>
       </c>
       <c r="C2359" t="n">
-        <v>0.4600038564335904</v>
+        <v>0.115879242768003</v>
       </c>
     </row>
     <row r="2360">
       <c r="A2360" t="n">
-        <v>0.4117983696065982</v>
+        <v>0.2389642734729595</v>
       </c>
       <c r="B2360" t="n">
-        <v>0.2634517280254261</v>
+        <v>0.2401502003884581</v>
       </c>
       <c r="C2360" t="n">
-        <v>0.3247499023679757</v>
+        <v>0.5208855261385824</v>
       </c>
     </row>
     <row r="2361">
       <c r="A2361" t="n">
-        <v>0.7032202695438542</v>
+        <v>0.6239036311688189</v>
       </c>
       <c r="B2361" t="n">
-        <v>0.1789666844016239</v>
+        <v>0.2140297210063437</v>
       </c>
       <c r="C2361" t="n">
-        <v>0.1178130460545219</v>
+        <v>0.1620666478248375</v>
       </c>
     </row>
     <row r="2362">
       <c r="A2362" t="n">
-        <v>0.4457959047034536</v>
+        <v>0.8060310558861845</v>
       </c>
       <c r="B2362" t="n">
-        <v>0.2788595659208838</v>
+        <v>0.1212900280372265</v>
       </c>
       <c r="C2362" t="n">
-        <v>0.2753445293756625</v>
+        <v>0.07267891607658901</v>
       </c>
     </row>
     <row r="2363">
       <c r="A2363" t="n">
-        <v>0.2912248230995201</v>
+        <v>0.6097629175489302</v>
       </c>
       <c r="B2363" t="n">
-        <v>0.2733873026846745</v>
+        <v>0.2013872516831749</v>
       </c>
       <c r="C2363" t="n">
-        <v>0.4353878742158054</v>
+        <v>0.188849830767895</v>
       </c>
     </row>
     <row r="2364">
       <c r="A2364" t="n">
-        <v>0.3101478154025677</v>
+        <v>0.7508040831582646</v>
       </c>
       <c r="B2364" t="n">
-        <v>0.2767774808339371</v>
+        <v>0.1539124321656916</v>
       </c>
       <c r="C2364" t="n">
-        <v>0.4130747037634953</v>
+        <v>0.09528348467604388</v>
       </c>
     </row>
     <row r="2365">
       <c r="A2365" t="n">
-        <v>0.1179518645032973</v>
+        <v>0.6463291238137986</v>
       </c>
       <c r="B2365" t="n">
-        <v>0.1719167698316032</v>
+        <v>0.2008352144296621</v>
       </c>
       <c r="C2365" t="n">
-        <v>0.7101313656650995</v>
+        <v>0.1528356617565393</v>
       </c>
     </row>
     <row r="2366">
       <c r="A2366" t="n">
-        <v>0.8771890162926371</v>
+        <v>0.5318044025338795</v>
       </c>
       <c r="B2366" t="n">
-        <v>0.08447833074104889</v>
+        <v>0.2368211856305849</v>
       </c>
       <c r="C2366" t="n">
-        <v>0.03833265296631409</v>
+        <v>0.2313744118355355</v>
       </c>
     </row>
     <row r="2367">
       <c r="A2367" t="n">
-        <v>0.5805376958138433</v>
+        <v>0.4648062809942835</v>
       </c>
       <c r="B2367" t="n">
-        <v>0.2289786312408609</v>
+        <v>0.2336061685185387</v>
       </c>
       <c r="C2367" t="n">
-        <v>0.1904836729452958</v>
+        <v>0.3015875504871778</v>
       </c>
     </row>
     <row r="2368">
       <c r="A2368" t="n">
-        <v>0.6764199512497624</v>
+        <v>0.2733245367333059</v>
       </c>
       <c r="B2368" t="n">
-        <v>0.1899441883307414</v>
+        <v>0.2666716068331038</v>
       </c>
       <c r="C2368" t="n">
-        <v>0.1336358604194962</v>
+        <v>0.4600038564335904</v>
       </c>
     </row>
     <row r="2369">
       <c r="A2369" t="n">
-        <v>0.2549477479948511</v>
+        <v>0.4117983696065982</v>
       </c>
       <c r="B2369" t="n">
-        <v>0.25948239173389</v>
+        <v>0.2634517280254261</v>
       </c>
       <c r="C2369" t="n">
-        <v>0.4855698602712588</v>
+        <v>0.3247499023679757</v>
       </c>
     </row>
     <row r="2370">
       <c r="A2370" t="n">
-        <v>0.5293019025240657</v>
+        <v>0.7032202695438542</v>
       </c>
       <c r="B2370" t="n">
-        <v>0.2589090174082216</v>
+        <v>0.1789666844016239</v>
       </c>
       <c r="C2370" t="n">
-        <v>0.2117890800677127</v>
+        <v>0.1178130460545219</v>
       </c>
     </row>
     <row r="2371">
       <c r="A2371" t="n">
-        <v>0.4524499752527752</v>
+        <v>0.4457959047034536</v>
       </c>
       <c r="B2371" t="n">
-        <v>0.2703528247189421</v>
+        <v>0.2788595659208838</v>
       </c>
       <c r="C2371" t="n">
-        <v>0.2771972000282825</v>
+        <v>0.2753445293756625</v>
       </c>
     </row>
     <row r="2372">
       <c r="A2372" t="n">
-        <v>0.3194189414403908</v>
+        <v>0.2912248230995201</v>
       </c>
       <c r="B2372" t="n">
-        <v>0.263488556513479</v>
+        <v>0.2733873026846745</v>
       </c>
       <c r="C2372" t="n">
-        <v>0.4170925020461301</v>
+        <v>0.4353878742158054</v>
       </c>
     </row>
     <row r="2373">
       <c r="A2373" t="n">
-        <v>0.5114098604973089</v>
+        <v>0.3101478154025677</v>
       </c>
       <c r="B2373" t="n">
-        <v>0.2551125636148738</v>
+        <v>0.2767774808339371</v>
       </c>
       <c r="C2373" t="n">
-        <v>0.2334775758878173</v>
+        <v>0.4130747037634953</v>
       </c>
     </row>
     <row r="2374">
       <c r="A2374" t="n">
-        <v>0.41694120234752</v>
+        <v>0.1179518645032973</v>
       </c>
       <c r="B2374" t="n">
-        <v>0.2923020032400904</v>
+        <v>0.1719167698316032</v>
       </c>
       <c r="C2374" t="n">
-        <v>0.2907567944123896</v>
+        <v>0.7101313656650995</v>
       </c>
     </row>
     <row r="2375">
       <c r="A2375" t="n">
-        <v>0.110732268167942</v>
+        <v>0.8771890162926371</v>
       </c>
       <c r="B2375" t="n">
-        <v>0.1845537802799033</v>
+        <v>0.08447833074104889</v>
       </c>
       <c r="C2375" t="n">
-        <v>0.7047139515521548</v>
+        <v>0.03833265296631409</v>
       </c>
     </row>
     <row r="2376">
       <c r="A2376" t="n">
-        <v>0.2807582485465553</v>
+        <v>0.5805376958138433</v>
       </c>
       <c r="B2376" t="n">
-        <v>0.2783738897478585</v>
+        <v>0.2289786312408609</v>
       </c>
       <c r="C2376" t="n">
-        <v>0.4408678617055862</v>
+        <v>0.1904836729452958</v>
       </c>
     </row>
     <row r="2377">
       <c r="A2377" t="n">
-        <v>0.2712294185144576</v>
+        <v>0.6764199512497624</v>
       </c>
       <c r="B2377" t="n">
-        <v>0.2723478903433832</v>
+        <v>0.1899441883307414</v>
       </c>
       <c r="C2377" t="n">
-        <v>0.4564226911421591</v>
+        <v>0.1336358604194962</v>
       </c>
     </row>
     <row r="2378">
       <c r="A2378" t="n">
-        <v>0.6136014730344417</v>
+        <v>0.5293019025240657</v>
       </c>
       <c r="B2378" t="n">
-        <v>0.217540423388817</v>
+        <v>0.2589090174082216</v>
       </c>
       <c r="C2378" t="n">
-        <v>0.1688581035767415</v>
+        <v>0.2117890800677127</v>
       </c>
     </row>
     <row r="2379">
       <c r="A2379" t="n">
+        <v>0.2549477479948511</v>
+      </c>
+      <c r="B2379" t="n">
+        <v>0.25948239173389</v>
+      </c>
+      <c r="C2379" t="n">
+        <v>0.4855698602712588</v>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="A2380" t="n">
+        <v>0.4524499752527752</v>
+      </c>
+      <c r="B2380" t="n">
+        <v>0.2703528247189421</v>
+      </c>
+      <c r="C2380" t="n">
+        <v>0.2771972000282825</v>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="A2381" t="n">
+        <v>0.3194189414403908</v>
+      </c>
+      <c r="B2381" t="n">
+        <v>0.263488556513479</v>
+      </c>
+      <c r="C2381" t="n">
+        <v>0.4170925020461301</v>
+      </c>
+    </row>
+    <row r="2382">
+      <c r="A2382" t="n">
+        <v>0.5114098604973089</v>
+      </c>
+      <c r="B2382" t="n">
+        <v>0.2551125636148738</v>
+      </c>
+      <c r="C2382" t="n">
+        <v>0.2334775758878173</v>
+      </c>
+    </row>
+    <row r="2383">
+      <c r="A2383" t="n">
+        <v>0.41694120234752</v>
+      </c>
+      <c r="B2383" t="n">
+        <v>0.2923020032400904</v>
+      </c>
+      <c r="C2383" t="n">
+        <v>0.2907567944123896</v>
+      </c>
+    </row>
+    <row r="2384">
+      <c r="A2384" t="n">
+        <v>0.110732268167942</v>
+      </c>
+      <c r="B2384" t="n">
+        <v>0.1845537802799033</v>
+      </c>
+      <c r="C2384" t="n">
+        <v>0.7047139515521548</v>
+      </c>
+    </row>
+    <row r="2385">
+      <c r="A2385" t="n">
+        <v>0.2807582485465553</v>
+      </c>
+      <c r="B2385" t="n">
+        <v>0.2783738897478585</v>
+      </c>
+      <c r="C2385" t="n">
+        <v>0.4408678617055862</v>
+      </c>
+    </row>
+    <row r="2386">
+      <c r="A2386" t="n">
+        <v>0.2712294185144576</v>
+      </c>
+      <c r="B2386" t="n">
+        <v>0.2723478903433832</v>
+      </c>
+      <c r="C2386" t="n">
+        <v>0.4564226911421591</v>
+      </c>
+    </row>
+    <row r="2387">
+      <c r="A2387" t="n">
+        <v>0.6136014730344417</v>
+      </c>
+      <c r="B2387" t="n">
+        <v>0.217540423388817</v>
+      </c>
+      <c r="C2387" t="n">
+        <v>0.1688581035767415</v>
+      </c>
+    </row>
+    <row r="2388">
+      <c r="A2388" t="n">
         <v>0.3531671690714473</v>
       </c>
-      <c r="B2379" t="n">
+      <c r="B2388" t="n">
         <v>0.2564241001896189</v>
       </c>
-      <c r="C2379" t="n">
+      <c r="C2388" t="n">
         <v>0.3904087307389339</v>
       </c>
     </row>

--- a/French Ligue 1/Y.xlsx
+++ b/French Ligue 1/Y.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2388"/>
+  <dimension ref="A1:C2395"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26702,6 +26702,83 @@
         <v>0.3904087307389339</v>
       </c>
     </row>
+    <row r="2389">
+      <c r="A2389" t="n">
+        <v>0.5634148050645568</v>
+      </c>
+      <c r="B2389" t="n">
+        <v>0.2461786331084314</v>
+      </c>
+      <c r="C2389" t="n">
+        <v>0.1904065618270118</v>
+      </c>
+    </row>
+    <row r="2390">
+      <c r="A2390" t="n">
+        <v>0.1902063702872421</v>
+      </c>
+      <c r="B2390" t="n">
+        <v>0.2189108142277712</v>
+      </c>
+      <c r="C2390" t="n">
+        <v>0.5908828154849867</v>
+      </c>
+    </row>
+    <row r="2391">
+      <c r="A2391" t="n">
+        <v>0.5298987969939679</v>
+      </c>
+      <c r="B2391" t="n">
+        <v>0.2485525300616989</v>
+      </c>
+      <c r="C2391" t="n">
+        <v>0.2215486729443331</v>
+      </c>
+    </row>
+    <row r="2392">
+      <c r="A2392" t="n">
+        <v>0.5879359002757906</v>
+      </c>
+      <c r="B2392" t="n">
+        <v>0.2316673740384957</v>
+      </c>
+      <c r="C2392" t="n">
+        <v>0.1803967256857139</v>
+      </c>
+    </row>
+    <row r="2393">
+      <c r="A2393" t="n">
+        <v>0.4148637872885567</v>
+      </c>
+      <c r="B2393" t="n">
+        <v>0.2815400402624906</v>
+      </c>
+      <c r="C2393" t="n">
+        <v>0.3035961724489529</v>
+      </c>
+    </row>
+    <row r="2394">
+      <c r="A2394" t="n">
+        <v>0.7192850332988583</v>
+      </c>
+      <c r="B2394" t="n">
+        <v>0.1638470621757697</v>
+      </c>
+      <c r="C2394" t="n">
+        <v>0.116867904525372</v>
+      </c>
+    </row>
+    <row r="2395">
+      <c r="A2395" t="n">
+        <v>0.3522275411278556</v>
+      </c>
+      <c r="B2395" t="n">
+        <v>0.2692743610336626</v>
+      </c>
+      <c r="C2395" t="n">
+        <v>0.3784980978384817</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
